--- a/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,73; 91,53</t>
+          <t>34,75; 85,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,87; 73,95</t>
+          <t>29,45; 74,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,27; 87,87</t>
+          <t>14,17; 87,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,36; 100,0</t>
+          <t>34,67; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,34; 100,0</t>
+          <t>65,39; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,89; 84,02</t>
+          <t>34,48; 84,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 74,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,01; 100,0</t>
+          <t>60,2; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60,27; 89,91</t>
+          <t>58,92; 89,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,31; 71,95</t>
+          <t>38,32; 70,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,37; 72,59</t>
+          <t>15,8; 74,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,78; 97,52</t>
+          <t>67,71; 97,76</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,01; 88,78</t>
+          <t>63,23; 88,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,71; 72,14</t>
+          <t>50,19; 72,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,06; 62,86</t>
+          <t>32,66; 61,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71,36; 91,98</t>
+          <t>72,52; 91,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,34; 86,24</t>
+          <t>67,12; 85,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,09; 71,69</t>
+          <t>52,85; 71,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,18; 70,8</t>
+          <t>44,92; 71,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,97; 85,72</t>
+          <t>60,94; 85,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,9; 85,12</t>
+          <t>70,0; 84,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,38; 68,85</t>
+          <t>54,77; 69,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,63; 63,47</t>
+          <t>44,62; 63,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,54; 85,52</t>
+          <t>70,24; 85,84</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,08; 79,58</t>
+          <t>41,07; 80,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50,78; 87,61</t>
+          <t>53,89; 90,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,55; 80,46</t>
+          <t>35,38; 82,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,95; 88,84</t>
+          <t>53,12; 88,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,12; 96,6</t>
+          <t>74,13; 96,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,54; 84,23</t>
+          <t>45,73; 83,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 78,79</t>
+          <t>25,8; 78,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,02; 83,42</t>
+          <t>48,83; 84,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,32; 86,99</t>
+          <t>63,01; 87,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,03; 82,16</t>
+          <t>54,85; 81,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,57; 71,81</t>
+          <t>39,51; 72,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>58,13; 82,56</t>
+          <t>57,48; 82,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,04; 79,53</t>
+          <t>60,4; 80,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,97; 70,41</t>
+          <t>53,45; 71,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,66; 62,55</t>
+          <t>39,46; 64,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,22; 88,39</t>
+          <t>70,86; 89,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,61; 87,96</t>
+          <t>75,03; 88,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,32; 70,98</t>
+          <t>54,88; 71,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,35; 66,85</t>
+          <t>42,5; 65,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,16; 83,51</t>
+          <t>64,66; 82,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,76; 83,16</t>
+          <t>71,64; 83,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,39; 68,05</t>
+          <t>56,71; 68,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,34; 61,22</t>
+          <t>44,71; 61,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,55; 83,15</t>
+          <t>69,98; 82,88</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6703</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7850</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>9562</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14188</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13699</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>17412</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2717; 6702</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3754; 9432</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>631; 3877</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3253; 9382</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6779; 10367</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3983; 9756</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2075</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6567; 10908</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10715; 16354</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9311; 17116</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1141; 5364</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>13738; 19836</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>23684</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14854</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31468</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42472</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22521</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>48417</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>65082</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>75875</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>37375</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>79885</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19322; 26970</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27233; 39069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10150; 19158</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27248; 34556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>35416; 45366</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>35883; 48492</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17300; 27592</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>40106; 56268</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>58325; 70687</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>66897; 84710</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>31052; 44342</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>72617; 88752</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11168</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6853</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16969</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12538</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15468</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27457</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23707</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12117</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>27691</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7063; 13777</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8213; 13840</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4103; 9587</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8814; 14676</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14081; 18354</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8615; 15727</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2621; 7967</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>10891; 18768</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>22805; 31576</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18694; 27746</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8595; 15813</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22357; 32111</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>39396</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51274</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24192</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51540</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>73448</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>106727</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113281</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>52621</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>124989</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33568; 44653</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>43961; 58425</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18596; 30253</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45028; 56624</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>61625; 72284</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>53943; 70547</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>21865; 33701</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>64030; 82179</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>98650; 114986</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>102383; 123457</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>44075; 60958</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>113774; 134739</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,75; 85,73</t>
+          <t>37,34; 91,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,45; 74,0</t>
+          <t>27,86; 73,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 87,15</t>
+          <t>15,33; 87,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,67; 100,0</t>
+          <t>42,14; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,39; 100,0</t>
+          <t>59,64; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,48; 84,46</t>
+          <t>34,32; 82,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,83</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,2; 100,0</t>
+          <t>63,27; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,92; 89,93</t>
+          <t>59,86; 89,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,32; 70,44</t>
+          <t>39,19; 71,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 74,28</t>
+          <t>15,78; 78,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,71; 97,76</t>
+          <t>63,72; 96,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,23; 88,25</t>
+          <t>63,53; 88,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,19; 72,01</t>
+          <t>50,52; 71,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,66; 61,65</t>
+          <t>32,77; 63,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,52; 91,97</t>
+          <t>72,31; 92,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,12; 85,97</t>
+          <t>68,71; 87,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,85; 71,42</t>
+          <t>53,03; 70,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,92; 71,64</t>
+          <t>45,14; 70,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,94; 85,49</t>
+          <t>62,74; 85,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,0; 84,83</t>
+          <t>70,24; 85,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,77; 69,35</t>
+          <t>54,55; 69,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,62; 63,72</t>
+          <t>43,54; 62,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,24; 85,84</t>
+          <t>68,32; 85,15</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,07; 80,12</t>
+          <t>37,66; 79,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,89; 90,82</t>
+          <t>51,44; 89,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,38; 82,67</t>
+          <t>36,53; 81,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,12; 88,45</t>
+          <t>51,18; 88,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,13; 96,62</t>
+          <t>74,32; 96,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,73; 83,48</t>
+          <t>47,13; 84,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,8; 78,42</t>
+          <t>26,31; 78,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,83; 84,15</t>
+          <t>48,06; 82,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,01; 87,24</t>
+          <t>63,38; 86,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54,85; 81,41</t>
+          <t>56,33; 81,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 72,69</t>
+          <t>38,55; 74,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,48; 82,55</t>
+          <t>57,33; 81,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,4; 80,35</t>
+          <t>60,24; 79,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,45; 71,04</t>
+          <t>54,06; 70,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,46; 64,2</t>
+          <t>39,33; 62,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70,86; 89,1</t>
+          <t>71,89; 89,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,03; 88,01</t>
+          <t>74,32; 88,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,88; 71,78</t>
+          <t>55,36; 70,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,5; 65,51</t>
+          <t>44,22; 66,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,66; 82,99</t>
+          <t>64,55; 83,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,64; 83,5</t>
+          <t>71,47; 82,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 68,39</t>
+          <t>56,51; 67,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44,71; 61,84</t>
+          <t>46,0; 61,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,98; 82,88</t>
+          <t>70,47; 83,51</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2717; 6702</t>
+          <t>2919; 7178</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3754; 9432</t>
+          <t>3551; 9348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>631; 3877</t>
+          <t>682; 3901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3253; 9382</t>
+          <t>3954; 9382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6779; 10367</t>
+          <t>6183; 10367</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3983; 9756</t>
+          <t>3964; 9573</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6567; 10908</t>
+          <t>6902; 10908</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10715; 16354</t>
+          <t>10886; 16335</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9311; 17116</t>
+          <t>9522; 17489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1141; 5364</t>
+          <t>1140; 5670</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13738; 19836</t>
+          <t>12928; 19647</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19322; 26970</t>
+          <t>19414; 27023</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27233; 39069</t>
+          <t>27413; 38590</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10150; 19158</t>
+          <t>10183; 19603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27248; 34556</t>
+          <t>27170; 34637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35416; 45366</t>
+          <t>36256; 45987</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35883; 48492</t>
+          <t>36001; 48172</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17300; 27592</t>
+          <t>17386; 27278</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40106; 56268</t>
+          <t>41295; 56200</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58325; 70687</t>
+          <t>58529; 71112</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66897; 84710</t>
+          <t>66629; 84604</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31052; 44342</t>
+          <t>30300; 43668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72617; 88752</t>
+          <t>70640; 88032</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7063; 13777</t>
+          <t>6476; 13585</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8213; 13840</t>
+          <t>7840; 13692</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4103; 9587</t>
+          <t>4237; 9394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8814; 14676</t>
+          <t>8491; 14750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14081; 18354</t>
+          <t>14117; 18351</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8615; 15727</t>
+          <t>8880; 15974</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2621; 7967</t>
+          <t>2673; 8023</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10891; 18768</t>
+          <t>10720; 18494</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22805; 31576</t>
+          <t>22938; 31271</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18694; 27746</t>
+          <t>19197; 27650</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8595; 15813</t>
+          <t>8387; 16137</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22357; 32111</t>
+          <t>22300; 31881</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33568; 44653</t>
+          <t>33479; 44264</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43961; 58425</t>
+          <t>44459; 58200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18596; 30253</t>
+          <t>18533; 29516</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45028; 56624</t>
+          <t>45687; 56596</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61625; 72284</t>
+          <t>61042; 72400</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53943; 70547</t>
+          <t>54405; 69358</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21865; 33701</t>
+          <t>22748; 34242</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64030; 82179</t>
+          <t>63923; 82207</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98650; 114986</t>
+          <t>98413; 114016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102383; 123457</t>
+          <t>102009; 122446</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44075; 60958</t>
+          <t>45337; 61043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>113774; 134739</t>
+          <t>114571; 135763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP09B02-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>66,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>52,59%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>55,85%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,34; 91,81</t>
+          <t>58,34; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 73,34</t>
+          <t>34,89; 84,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,33; 87,68</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,14; 100,0</t>
+          <t>66,82; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,64; 100,0</t>
+          <t>30,73; 91,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,32; 82,87</t>
+          <t>30,87; 73,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>14,27; 87,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,27; 100,0</t>
+          <t>21,46; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,86; 89,83</t>
+          <t>60,27; 89,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,19; 71,98</t>
+          <t>40,31; 71,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 78,5</t>
+          <t>15,37; 72,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,72; 96,83</t>
+          <t>61,02; 94,99</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>72,77%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>77,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>61,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>47,8%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>62,56%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,53; 88,43</t>
+          <t>68,34; 86,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50,52; 71,13</t>
+          <t>53,09; 71,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,77; 63,08</t>
+          <t>45,18; 70,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,31; 92,19</t>
+          <t>62,27; 85,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,71; 87,15</t>
+          <t>64,01; 88,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,03; 70,95</t>
+          <t>49,71; 72,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,14; 70,82</t>
+          <t>32,06; 62,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>62,74; 85,39</t>
+          <t>71,02; 91,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>70,24; 85,34</t>
+          <t>70,9; 85,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,55; 69,26</t>
+          <t>54,38; 68,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 62,75</t>
+          <t>44,63; 63,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,32; 85,15</t>
+          <t>69,14; 84,7</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51,81%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>60,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>73,28%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>59,09%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,66%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,66; 79,0</t>
+          <t>72,12; 96,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,44; 89,84</t>
+          <t>45,54; 84,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,53; 81,0</t>
+          <t>30,32; 78,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,18; 88,89</t>
+          <t>50,66; 83,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74,32; 96,6</t>
+          <t>41,08; 79,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,13; 84,79</t>
+          <t>50,78; 87,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,31; 78,97</t>
+          <t>33,55; 80,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,06; 82,92</t>
+          <t>51,24; 88,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,38; 86,4</t>
+          <t>62,32; 86,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56,33; 81,13</t>
+          <t>56,03; 82,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,55; 74,17</t>
+          <t>38,57; 71,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,33; 81,96</t>
+          <t>56,75; 82,41</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>70,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>51,34%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81,98%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,05%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,24; 79,65</t>
+          <t>74,61; 87,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,06; 70,77</t>
+          <t>55,32; 70,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,33; 62,64</t>
+          <t>43,35; 66,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,89; 89,06</t>
+          <t>65,36; 82,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,32; 88,15</t>
+          <t>59,04; 79,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,36; 70,57</t>
+          <t>52,97; 70,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,22; 66,56</t>
+          <t>39,66; 62,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,55; 83,01</t>
+          <t>69,21; 86,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>71,47; 82,8</t>
+          <t>71,76; 83,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,51; 67,83</t>
+          <t>56,39; 68,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46,0; 61,93</t>
+          <t>45,34; 61,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,47; 83,51</t>
+          <t>69,61; 82,22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5226</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6703</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2485</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7850</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>11557</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2919; 7178</t>
+          <t>6048; 10367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3551; 9348</t>
+          <t>4031; 9705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>682; 3901</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3954; 9382</t>
+          <t>6458; 9664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6183; 10367</t>
+          <t>2402; 7156</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3964; 9573</t>
+          <t>3934; 9425</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2773</t>
+          <t>635; 3909</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6902; 10908</t>
+          <t>941; 4383</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10886; 16335</t>
+          <t>10960; 16351</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9522; 17489</t>
+          <t>9794; 17481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1140; 5670</t>
+          <t>1110; 5242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12928; 19647</t>
+          <t>8572; 13344</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41397</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>42472</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22521</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43243</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23684</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>33403</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14854</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31468</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42472</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22521</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79885</t>
+          <t>74598</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19414; 27023</t>
+          <t>36062; 45506</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27413; 38590</t>
+          <t>36044; 48675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10183; 19603</t>
+          <t>17399; 27269</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27170; 34637</t>
+          <t>37007; 50565</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36256; 45987</t>
+          <t>19561; 27132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36001; 48172</t>
+          <t>26970; 39141</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17386; 27278</t>
+          <t>9963; 19535</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41295; 56200</t>
+          <t>26623; 34426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58529; 71112</t>
+          <t>59080; 70930</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66629; 84604</t>
+          <t>66430; 84097</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30300; 43668</t>
+          <t>31058; 44172</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70640; 88032</t>
+          <t>67006; 82086</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16969</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12538</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13775</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10486</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11168</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6853</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12222</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16969</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12538</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5263</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>12595</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>26371</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6476; 13585</t>
+          <t>13699; 18350</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7840; 13692</t>
+          <t>8579; 15869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4237; 9394</t>
+          <t>3080; 8004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8491; 14750</t>
+          <t>10021; 16599</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14117; 18351</t>
+          <t>7065; 13685</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8880; 15974</t>
+          <t>7740; 13351</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2673; 8023</t>
+          <t>3891; 9331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10720; 18494</t>
+          <t>8819; 15305</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22938; 31271</t>
+          <t>22555; 31484</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19197; 27650</t>
+          <t>19096; 28003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8387; 16137</t>
+          <t>8391; 15623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22300; 31881</t>
+          <t>20995; 30485</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67331</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>28429</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65683</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>39396</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51274</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>24192</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51540</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67331</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62007</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>124989</t>
+          <t>112525</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33479; 44264</t>
+          <t>61277; 72241</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44459; 58200</t>
+          <t>54369; 69759</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18533; 29516</t>
+          <t>22300; 34394</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45687; 56596</t>
+          <t>58089; 73728</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61042; 72400</t>
+          <t>32809; 44199</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54405; 69358</t>
+          <t>43562; 57908</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22748; 34242</t>
+          <t>18689; 29474</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63923; 82207</t>
+          <t>40889; 51248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98413; 114016</t>
+          <t>98818; 114513</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102009; 122446</t>
+          <t>101791; 122853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45337; 61043</t>
+          <t>44687; 60342</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>114571; 135763</t>
+          <t>102983; 121641</t>
         </is>
       </c>
     </row>
